--- a/output/pdf_financials_xlsx/OMR.H.xlsx
+++ b/output/pdf_financials_xlsx/OMR.H.xlsx
@@ -916,34 +916,34 @@
         <v>0.017239</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.077958</v>
+        <v>0.146802</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.10712</v>
+        <v>0.135754</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.024623</v>
+        <v>0.048428</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.010616</v>
+        <v>0.035331</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.013474</v>
+        <v>0.037106</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.014321</v>
+        <v>0.036814</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.083887</v>
+        <v>0.115626</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.017917</v>
+        <v>0.037715</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.009960999999999999</v>
+        <v>0.027427</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.028488</v>
+        <v>0.044213</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>0.165384</v>
@@ -952,16 +952,16 @@
         <v>0.097165</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.009801000000000001</v>
+        <v>0.063571</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.002872</v>
+        <v>0.037247</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.002761</v>
+        <v>0.041684</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.002769</v>
+        <v>0.038749</v>
       </c>
     </row>
     <row r="11">
@@ -986,10 +986,10 @@
         <v>-0.035331</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.013474</v>
+        <v>-0.037106</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.014321</v>
+        <v>-0.036814</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>-0.115626</v>
@@ -1010,16 +1010,16 @@
         <v>-0.097165</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.009801000000000001</v>
+        <v>-0.063571</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.002872</v>
+        <v>-0.037247</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.002761</v>
+        <v>-0.041684</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.002769</v>
+        <v>-0.038749</v>
       </c>
     </row>
     <row r="12">
@@ -1032,13 +1032,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>3.6e-05</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>4e-06</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>3.9e-05</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1978,13 +1978,13 @@
         <v>-0.017239</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.146766</v>
+        <v>-0.146802</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.08575000000000001</v>
+        <v>-0.085754</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.048389</v>
+        <v>-0.048428</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.035331</v>
@@ -2094,13 +2094,13 @@
         <v>-0.017239</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.146766</v>
+        <v>-0.146802</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.08575000000000001</v>
+        <v>-0.085754</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.048389</v>
+        <v>-0.048428</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.035331</v>
@@ -2446,7 +2446,7 @@
         <v>0.000319</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.000104</v>
       </c>
     </row>
     <row r="35">
@@ -2562,7 +2562,7 @@
         <v>0.000319</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.000104</v>
       </c>
     </row>
     <row r="37">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -24121,7 +24121,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -24608,7 +24608,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -27185,7 +27185,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E190" s="5" t="n">
@@ -29765,7 +29765,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">

--- a/output/pdf_financials_xlsx/OMR.H.xlsx
+++ b/output/pdf_financials_xlsx/OMR.H.xlsx
@@ -742,34 +742,34 @@
         <v>0.017239</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.077958</v>
+        <v>0.07947899999999999</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.10712</v>
+        <v>0.107852</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.024623</v>
+        <v>0.025062</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.010616</v>
+        <v>0.011202</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.013474</v>
+        <v>0.014358</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.014321</v>
+        <v>0.015062</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.083887</v>
+        <v>0.085189</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.017917</v>
+        <v>0.018842</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.009960999999999999</v>
+        <v>0.010258</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.024292</v>
+        <v>0.024542</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>0.06952800000000001</v>
@@ -6473,10 +6473,10 @@
         <v>0</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003135</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003069</v>
       </c>
       <c r="P101" s="3" t="n">
         <v>0</v>
@@ -6763,10 +6763,10 @@
         <v>0.056405</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.019485</v>
+        <v>0.01635</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0.047897</v>
+        <v>0.044828</v>
       </c>
       <c r="P106" s="3" t="n">
         <v>0.020413</v>
@@ -15854,7 +15854,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -21628,7 +21632,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E133" s="5" t="n">
         <v>0.11996</v>
       </c>
@@ -26467,7 +26475,11 @@
           <t>Office supplies and office expenses</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
